--- a/Dubai.xlsx
+++ b/Dubai.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KHALED\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\datanalysis\Hotels\Final\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8976"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22992" windowHeight="8880"/>
   </bookViews>
   <sheets>
     <sheet name="Dubai" sheetId="1" r:id="rId1"/>
@@ -3286,11 +3286,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3628,7 +3627,7 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">

--- a/Dubai.xlsx
+++ b/Dubai.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\datanalysis\Hotels\Final\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KHALED\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -3622,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -3683,11 +3683,11 @@
       <c r="A2" t="s">
         <v>64</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
       </c>
       <c r="D2" t="s">
         <v>308</v>
@@ -3738,11 +3738,11 @@
       <c r="A3" t="s">
         <v>65</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3">
         <v>7.8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
       </c>
       <c r="D3" t="s">
         <v>311</v>
@@ -3793,11 +3793,11 @@
       <c r="A4" t="s">
         <v>66</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4">
         <v>9.3000000000000007</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
       </c>
       <c r="D4" t="s">
         <v>314</v>
@@ -3848,11 +3848,11 @@
       <c r="A5" t="s">
         <v>67</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5">
         <v>9.4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
       </c>
       <c r="D5" t="s">
         <v>316</v>
@@ -3906,7 +3906,7 @@
       <c r="A6" t="s">
         <v>68</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>6.3</v>
       </c>
       <c r="D6" t="s">
@@ -3961,11 +3961,11 @@
       <c r="A7" t="s">
         <v>69</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7">
         <v>8.9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
       </c>
       <c r="D7" t="s">
         <v>320</v>
@@ -4016,11 +4016,11 @@
       <c r="A8" t="s">
         <v>70</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8">
         <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
       </c>
       <c r="D8" t="s">
         <v>323</v>
@@ -4074,11 +4074,11 @@
       <c r="A9" t="s">
         <v>71</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9">
         <v>8.9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
       </c>
       <c r="D9" t="s">
         <v>326</v>
@@ -4129,11 +4129,11 @@
       <c r="A10" t="s">
         <v>72</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10">
         <v>9.1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
       </c>
       <c r="D10" t="s">
         <v>329</v>
@@ -4184,11 +4184,11 @@
       <c r="A11" t="s">
         <v>73</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
       </c>
       <c r="D11" t="s">
         <v>332</v>
@@ -4239,7 +4239,7 @@
       <c r="A12" t="s">
         <v>74</v>
       </c>
-      <c r="B12">
+      <c r="C12">
         <v>7.2</v>
       </c>
       <c r="D12" t="s">
@@ -4294,11 +4294,11 @@
       <c r="A13" t="s">
         <v>75</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13">
         <v>8.6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
       </c>
       <c r="D13" t="s">
         <v>338</v>
@@ -4352,11 +4352,11 @@
       <c r="A14" t="s">
         <v>76</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14">
         <v>8.9</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
       </c>
       <c r="D14" t="s">
         <v>341</v>
@@ -4410,11 +4410,11 @@
       <c r="A15" t="s">
         <v>77</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
       </c>
       <c r="D15" t="s">
         <v>344</v>
@@ -4468,11 +4468,11 @@
       <c r="A16" t="s">
         <v>78</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16">
         <v>9.3000000000000007</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
       </c>
       <c r="D16" t="s">
         <v>347</v>
@@ -4526,11 +4526,11 @@
       <c r="A17" t="s">
         <v>79</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17">
         <v>9</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
       </c>
       <c r="D17" t="s">
         <v>350</v>
@@ -4584,11 +4584,11 @@
       <c r="A18" t="s">
         <v>80</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
         <v>8.1999999999999993</v>
-      </c>
-      <c r="C18" t="s">
-        <v>23</v>
       </c>
       <c r="D18" t="s">
         <v>353</v>
@@ -4639,11 +4639,11 @@
       <c r="A19" t="s">
         <v>81</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19">
         <v>9.1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>27</v>
       </c>
       <c r="D19" t="s">
         <v>356</v>
@@ -4697,7 +4697,7 @@
       <c r="A20" t="s">
         <v>82</v>
       </c>
-      <c r="B20">
+      <c r="C20">
         <v>7.2</v>
       </c>
       <c r="D20" t="s">
@@ -4752,7 +4752,7 @@
       <c r="A21" t="s">
         <v>83</v>
       </c>
-      <c r="B21">
+      <c r="C21">
         <v>7</v>
       </c>
       <c r="D21" t="s">
@@ -4807,11 +4807,11 @@
       <c r="A22" t="s">
         <v>84</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C22" t="s">
-        <v>23</v>
       </c>
       <c r="D22" t="s">
         <v>365</v>
@@ -4862,11 +4862,11 @@
       <c r="A23" t="s">
         <v>85</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C23" t="s">
-        <v>27</v>
       </c>
       <c r="D23" t="s">
         <v>52</v>
@@ -4917,11 +4917,11 @@
       <c r="A24" t="s">
         <v>86</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C24" t="s">
-        <v>23</v>
       </c>
       <c r="D24" t="s">
         <v>370</v>
@@ -4972,11 +4972,11 @@
       <c r="A25" t="s">
         <v>87</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C25" t="s">
-        <v>27</v>
       </c>
       <c r="D25" t="s">
         <v>373</v>
@@ -5027,11 +5027,11 @@
       <c r="A26" t="s">
         <v>88</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26">
         <v>7.9</v>
-      </c>
-      <c r="C26" t="s">
-        <v>32</v>
       </c>
       <c r="D26" t="s">
         <v>375</v>
@@ -5082,11 +5082,11 @@
       <c r="A27" t="s">
         <v>89</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C27" t="s">
-        <v>23</v>
       </c>
       <c r="D27" t="s">
         <v>378</v>
@@ -5137,11 +5137,11 @@
       <c r="A28" t="s">
         <v>90</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28">
         <v>8.6</v>
-      </c>
-      <c r="C28" t="s">
-        <v>27</v>
       </c>
       <c r="D28" t="s">
         <v>381</v>
@@ -5192,11 +5192,11 @@
       <c r="A29" t="s">
         <v>91</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C29" t="s">
-        <v>27</v>
       </c>
       <c r="D29" t="s">
         <v>383</v>
@@ -5250,11 +5250,11 @@
       <c r="A30" t="s">
         <v>92</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30">
         <v>8</v>
-      </c>
-      <c r="C30" t="s">
-        <v>23</v>
       </c>
       <c r="D30" t="s">
         <v>386</v>
@@ -5308,11 +5308,11 @@
       <c r="A31" t="s">
         <v>93</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31">
         <v>9</v>
-      </c>
-      <c r="C31" t="s">
-        <v>27</v>
       </c>
       <c r="D31" t="s">
         <v>388</v>
@@ -5366,11 +5366,11 @@
       <c r="A32" t="s">
         <v>94</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32">
         <v>8.5</v>
-      </c>
-      <c r="C32" t="s">
-        <v>27</v>
       </c>
       <c r="D32" t="s">
         <v>391</v>
@@ -5421,11 +5421,11 @@
       <c r="A33" t="s">
         <v>95</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C33" t="s">
-        <v>23</v>
       </c>
       <c r="D33" t="s">
         <v>394</v>
@@ -5476,11 +5476,11 @@
       <c r="A34" t="s">
         <v>96</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C34" t="s">
-        <v>27</v>
       </c>
       <c r="D34" t="s">
         <v>397</v>
@@ -5534,11 +5534,11 @@
       <c r="A35" t="s">
         <v>97</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35">
         <v>8.9</v>
-      </c>
-      <c r="C35" t="s">
-        <v>27</v>
       </c>
       <c r="D35" t="s">
         <v>400</v>
@@ -5589,7 +5589,7 @@
       <c r="A36" t="s">
         <v>98</v>
       </c>
-      <c r="B36">
+      <c r="C36">
         <v>7</v>
       </c>
       <c r="D36" t="s">
@@ -5644,11 +5644,11 @@
       <c r="A37" t="s">
         <v>99</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C37" t="s">
-        <v>23</v>
       </c>
       <c r="D37" t="s">
         <v>406</v>
@@ -5699,11 +5699,11 @@
       <c r="A38" t="s">
         <v>100</v>
       </c>
-      <c r="B38">
+      <c r="B38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38">
         <v>8.4</v>
-      </c>
-      <c r="C38" t="s">
-        <v>23</v>
       </c>
       <c r="D38" t="s">
         <v>409</v>
@@ -5754,11 +5754,11 @@
       <c r="A39" t="s">
         <v>101</v>
       </c>
-      <c r="B39">
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39">
         <v>8</v>
-      </c>
-      <c r="C39" t="s">
-        <v>23</v>
       </c>
       <c r="D39" t="s">
         <v>412</v>
@@ -5809,11 +5809,11 @@
       <c r="A40" t="s">
         <v>102</v>
       </c>
-      <c r="B40">
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40">
         <v>8.1999999999999993</v>
-      </c>
-      <c r="C40" t="s">
-        <v>23</v>
       </c>
       <c r="D40" t="s">
         <v>415</v>
@@ -5864,11 +5864,11 @@
       <c r="A41" t="s">
         <v>103</v>
       </c>
-      <c r="B41">
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41">
         <v>8</v>
-      </c>
-      <c r="C41" t="s">
-        <v>23</v>
       </c>
       <c r="D41" t="s">
         <v>418</v>
@@ -5919,11 +5919,11 @@
       <c r="A42" t="s">
         <v>104</v>
       </c>
-      <c r="B42">
+      <c r="B42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C42" t="s">
-        <v>27</v>
       </c>
       <c r="D42" t="s">
         <v>421</v>
@@ -5974,11 +5974,11 @@
       <c r="A43" t="s">
         <v>105</v>
       </c>
-      <c r="B43">
+      <c r="B43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43">
         <v>8</v>
-      </c>
-      <c r="C43" t="s">
-        <v>23</v>
       </c>
       <c r="D43" t="s">
         <v>424</v>
@@ -6032,11 +6032,11 @@
       <c r="A44" t="s">
         <v>106</v>
       </c>
-      <c r="B44">
+      <c r="B44" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44">
         <v>7.9</v>
-      </c>
-      <c r="C44" t="s">
-        <v>32</v>
       </c>
       <c r="D44" t="s">
         <v>427</v>
@@ -6087,7 +6087,7 @@
       <c r="A45" t="s">
         <v>107</v>
       </c>
-      <c r="B45">
+      <c r="C45">
         <v>7.1</v>
       </c>
       <c r="D45" t="s">
@@ -6139,11 +6139,11 @@
       <c r="A46" t="s">
         <v>108</v>
       </c>
-      <c r="B46">
+      <c r="B46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46">
         <v>7.6</v>
-      </c>
-      <c r="C46" t="s">
-        <v>32</v>
       </c>
       <c r="D46" t="s">
         <v>430</v>
@@ -6194,11 +6194,11 @@
       <c r="A47" t="s">
         <v>109</v>
       </c>
-      <c r="B47">
+      <c r="B47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47">
         <v>9.3000000000000007</v>
-      </c>
-      <c r="C47" t="s">
-        <v>27</v>
       </c>
       <c r="D47" t="s">
         <v>432</v>
@@ -6249,11 +6249,11 @@
       <c r="A48" t="s">
         <v>110</v>
       </c>
-      <c r="B48">
+      <c r="B48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48">
         <v>8.9</v>
-      </c>
-      <c r="C48" t="s">
-        <v>27</v>
       </c>
       <c r="D48" t="s">
         <v>434</v>
@@ -6307,11 +6307,11 @@
       <c r="A49" t="s">
         <v>111</v>
       </c>
-      <c r="B49">
+      <c r="B49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49">
         <v>9.1</v>
-      </c>
-      <c r="C49" t="s">
-        <v>27</v>
       </c>
       <c r="D49" t="s">
         <v>436</v>
@@ -6365,11 +6365,11 @@
       <c r="A50" t="s">
         <v>112</v>
       </c>
-      <c r="B50">
+      <c r="B50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C50">
         <v>9.1</v>
-      </c>
-      <c r="C50" t="s">
-        <v>27</v>
       </c>
       <c r="D50" t="s">
         <v>439</v>
@@ -6423,11 +6423,11 @@
       <c r="A51" t="s">
         <v>113</v>
       </c>
-      <c r="B51">
+      <c r="B51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C51" t="s">
-        <v>27</v>
       </c>
       <c r="D51" t="s">
         <v>441</v>
@@ -6481,11 +6481,11 @@
       <c r="A52" t="s">
         <v>114</v>
       </c>
-      <c r="B52">
+      <c r="B52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52">
         <v>9.1</v>
-      </c>
-      <c r="C52" t="s">
-        <v>27</v>
       </c>
       <c r="D52" t="s">
         <v>445</v>
@@ -6539,11 +6539,11 @@
       <c r="A53" t="s">
         <v>115</v>
       </c>
-      <c r="B53">
+      <c r="B53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53">
         <v>9.6</v>
-      </c>
-      <c r="C53" t="s">
-        <v>27</v>
       </c>
       <c r="D53" t="s">
         <v>448</v>
@@ -6582,11 +6582,11 @@
       <c r="A54" t="s">
         <v>115</v>
       </c>
-      <c r="B54">
+      <c r="B54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54">
         <v>9.6</v>
-      </c>
-      <c r="C54" t="s">
-        <v>27</v>
       </c>
       <c r="D54" t="s">
         <v>448</v>
@@ -6640,11 +6640,11 @@
       <c r="A55" t="s">
         <v>116</v>
       </c>
-      <c r="B55">
+      <c r="B55" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55">
         <v>7.7</v>
-      </c>
-      <c r="C55" t="s">
-        <v>32</v>
       </c>
       <c r="D55" t="s">
         <v>451</v>
@@ -6695,11 +6695,11 @@
       <c r="A56" t="s">
         <v>117</v>
       </c>
-      <c r="B56">
+      <c r="B56" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56">
         <v>9</v>
-      </c>
-      <c r="C56" t="s">
-        <v>27</v>
       </c>
       <c r="D56" t="s">
         <v>454</v>
@@ -6750,11 +6750,11 @@
       <c r="A57" t="s">
         <v>118</v>
       </c>
-      <c r="B57">
+      <c r="B57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C57" t="s">
-        <v>27</v>
       </c>
       <c r="D57" t="s">
         <v>456</v>
@@ -6805,11 +6805,11 @@
       <c r="A58" t="s">
         <v>119</v>
       </c>
-      <c r="B58">
+      <c r="B58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C58" t="s">
-        <v>27</v>
       </c>
       <c r="D58" t="s">
         <v>459</v>
@@ -6863,11 +6863,11 @@
       <c r="A59" t="s">
         <v>120</v>
       </c>
-      <c r="B59">
+      <c r="B59" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59">
         <v>9.4</v>
-      </c>
-      <c r="C59" t="s">
-        <v>27</v>
       </c>
       <c r="D59" t="s">
         <v>461</v>
@@ -6921,11 +6921,11 @@
       <c r="A60" t="s">
         <v>121</v>
       </c>
-      <c r="B60">
+      <c r="B60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C60" t="s">
-        <v>27</v>
       </c>
       <c r="D60" t="s">
         <v>464</v>
@@ -6979,11 +6979,11 @@
       <c r="A61" t="s">
         <v>122</v>
       </c>
-      <c r="B61">
+      <c r="B61" t="s">
+        <v>27</v>
+      </c>
+      <c r="C61">
         <v>9.3000000000000007</v>
-      </c>
-      <c r="C61" t="s">
-        <v>27</v>
       </c>
       <c r="D61" t="s">
         <v>466</v>
@@ -7037,11 +7037,11 @@
       <c r="A62" t="s">
         <v>123</v>
       </c>
-      <c r="B62">
+      <c r="B62" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62">
         <v>8.5</v>
-      </c>
-      <c r="C62" t="s">
-        <v>27</v>
       </c>
       <c r="D62" t="s">
         <v>469</v>
@@ -7095,11 +7095,11 @@
       <c r="A63" t="s">
         <v>124</v>
       </c>
-      <c r="B63">
+      <c r="B63" t="s">
+        <v>27</v>
+      </c>
+      <c r="C63">
         <v>9</v>
-      </c>
-      <c r="C63" t="s">
-        <v>27</v>
       </c>
       <c r="D63" t="s">
         <v>472</v>
@@ -7150,11 +7150,11 @@
       <c r="A64" t="s">
         <v>125</v>
       </c>
-      <c r="B64">
+      <c r="B64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C64" t="s">
-        <v>23</v>
       </c>
       <c r="D64" t="s">
         <v>474</v>
@@ -7205,11 +7205,11 @@
       <c r="A65" t="s">
         <v>126</v>
       </c>
-      <c r="B65">
+      <c r="B65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65">
         <v>9.1</v>
-      </c>
-      <c r="C65" t="s">
-        <v>27</v>
       </c>
       <c r="D65" t="s">
         <v>477</v>
@@ -7263,11 +7263,11 @@
       <c r="A66" t="s">
         <v>127</v>
       </c>
-      <c r="B66">
+      <c r="B66" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66">
         <v>9.3000000000000007</v>
-      </c>
-      <c r="C66" t="s">
-        <v>27</v>
       </c>
       <c r="D66" t="s">
         <v>480</v>
@@ -7318,11 +7318,11 @@
       <c r="A67" t="s">
         <v>128</v>
       </c>
-      <c r="B67">
+      <c r="B67" t="s">
+        <v>27</v>
+      </c>
+      <c r="C67">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C67" t="s">
-        <v>27</v>
       </c>
       <c r="D67" t="s">
         <v>482</v>
@@ -7376,11 +7376,11 @@
       <c r="A68" t="s">
         <v>129</v>
       </c>
-      <c r="B68">
+      <c r="B68" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68">
         <v>8.4</v>
-      </c>
-      <c r="C68" t="s">
-        <v>23</v>
       </c>
       <c r="D68" t="s">
         <v>485</v>
@@ -7431,11 +7431,11 @@
       <c r="A69" t="s">
         <v>130</v>
       </c>
-      <c r="B69">
+      <c r="B69" t="s">
+        <v>32</v>
+      </c>
+      <c r="C69">
         <v>7.8</v>
-      </c>
-      <c r="C69" t="s">
-        <v>32</v>
       </c>
       <c r="D69" t="s">
         <v>488</v>
@@ -7486,11 +7486,11 @@
       <c r="A70" t="s">
         <v>131</v>
       </c>
-      <c r="B70">
+      <c r="B70" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70">
         <v>7.8</v>
-      </c>
-      <c r="C70" t="s">
-        <v>32</v>
       </c>
       <c r="D70" t="s">
         <v>490</v>
@@ -7541,11 +7541,11 @@
       <c r="A71" t="s">
         <v>132</v>
       </c>
-      <c r="B71">
+      <c r="B71" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C71" t="s">
-        <v>27</v>
       </c>
       <c r="D71" t="s">
         <v>492</v>
@@ -7596,11 +7596,11 @@
       <c r="A72" t="s">
         <v>133</v>
       </c>
-      <c r="B72">
+      <c r="B72" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72">
         <v>8.6</v>
-      </c>
-      <c r="C72" t="s">
-        <v>27</v>
       </c>
       <c r="D72" t="s">
         <v>495</v>
@@ -7651,7 +7651,7 @@
       <c r="A73" t="s">
         <v>134</v>
       </c>
-      <c r="B73">
+      <c r="C73">
         <v>7.4</v>
       </c>
       <c r="D73" t="s">
@@ -7706,11 +7706,11 @@
       <c r="A74" t="s">
         <v>135</v>
       </c>
-      <c r="B74">
+      <c r="B74" t="s">
+        <v>27</v>
+      </c>
+      <c r="C74">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C74" t="s">
-        <v>27</v>
       </c>
       <c r="D74" t="s">
         <v>499</v>
@@ -7761,11 +7761,11 @@
       <c r="A75" t="s">
         <v>136</v>
       </c>
-      <c r="B75">
+      <c r="B75" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C75" t="s">
-        <v>23</v>
       </c>
       <c r="D75" t="s">
         <v>502</v>
@@ -7816,11 +7816,11 @@
       <c r="A76" t="s">
         <v>137</v>
       </c>
-      <c r="B76">
+      <c r="B76" t="s">
+        <v>32</v>
+      </c>
+      <c r="C76">
         <v>7.5</v>
-      </c>
-      <c r="C76" t="s">
-        <v>32</v>
       </c>
       <c r="D76" t="s">
         <v>504</v>
@@ -7874,7 +7874,7 @@
       <c r="A77" t="s">
         <v>138</v>
       </c>
-      <c r="B77">
+      <c r="C77">
         <v>6.5</v>
       </c>
       <c r="D77" t="s">
@@ -7929,11 +7929,11 @@
       <c r="A78" t="s">
         <v>139</v>
       </c>
-      <c r="B78">
+      <c r="B78" t="s">
+        <v>27</v>
+      </c>
+      <c r="C78">
         <v>8.9</v>
-      </c>
-      <c r="C78" t="s">
-        <v>27</v>
       </c>
       <c r="D78" t="s">
         <v>509</v>
@@ -7984,11 +7984,11 @@
       <c r="A79" t="s">
         <v>140</v>
       </c>
-      <c r="B79">
+      <c r="B79" t="s">
+        <v>27</v>
+      </c>
+      <c r="C79">
         <v>8.5</v>
-      </c>
-      <c r="C79" t="s">
-        <v>27</v>
       </c>
       <c r="D79" t="s">
         <v>512</v>
@@ -8042,11 +8042,11 @@
       <c r="A80" t="s">
         <v>141</v>
       </c>
-      <c r="B80">
+      <c r="B80" t="s">
+        <v>27</v>
+      </c>
+      <c r="C80">
         <v>8.9</v>
-      </c>
-      <c r="C80" t="s">
-        <v>27</v>
       </c>
       <c r="D80" t="s">
         <v>515</v>
@@ -8097,11 +8097,11 @@
       <c r="A81" t="s">
         <v>142</v>
       </c>
-      <c r="B81">
+      <c r="B81" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81">
         <v>8</v>
-      </c>
-      <c r="C81" t="s">
-        <v>23</v>
       </c>
       <c r="D81" t="s">
         <v>314</v>
@@ -8152,11 +8152,11 @@
       <c r="A82" t="s">
         <v>143</v>
       </c>
-      <c r="B82">
+      <c r="B82" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82">
         <v>8.1</v>
-      </c>
-      <c r="C82" t="s">
-        <v>23</v>
       </c>
       <c r="D82" t="s">
         <v>519</v>
@@ -8207,11 +8207,11 @@
       <c r="A83" t="s">
         <v>144</v>
       </c>
-      <c r="B83">
+      <c r="B83" t="s">
+        <v>27</v>
+      </c>
+      <c r="C83">
         <v>9.1999999999999993</v>
-      </c>
-      <c r="C83" t="s">
-        <v>27</v>
       </c>
       <c r="D83" t="s">
         <v>522</v>
@@ -8265,7 +8265,7 @@
       <c r="A84" t="s">
         <v>145</v>
       </c>
-      <c r="B84">
+      <c r="C84">
         <v>6.9</v>
       </c>
       <c r="D84" t="s">
@@ -8320,11 +8320,11 @@
       <c r="A85" t="s">
         <v>146</v>
       </c>
-      <c r="B85">
+      <c r="B85" t="s">
+        <v>32</v>
+      </c>
+      <c r="C85">
         <v>7.9</v>
-      </c>
-      <c r="C85" t="s">
-        <v>32</v>
       </c>
       <c r="D85" t="s">
         <v>527</v>
@@ -8378,11 +8378,11 @@
       <c r="A86" t="s">
         <v>147</v>
       </c>
-      <c r="B86">
+      <c r="B86" t="s">
+        <v>32</v>
+      </c>
+      <c r="C86">
         <v>7.7</v>
-      </c>
-      <c r="C86" t="s">
-        <v>32</v>
       </c>
       <c r="D86" t="s">
         <v>530</v>
@@ -8433,11 +8433,11 @@
       <c r="A87" t="s">
         <v>148</v>
       </c>
-      <c r="B87">
+      <c r="B87" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87">
         <v>9.5</v>
-      </c>
-      <c r="C87" t="s">
-        <v>27</v>
       </c>
       <c r="D87" t="s">
         <v>533</v>
@@ -8488,11 +8488,11 @@
       <c r="A88" t="s">
         <v>149</v>
       </c>
-      <c r="B88">
+      <c r="B88" t="s">
+        <v>32</v>
+      </c>
+      <c r="C88">
         <v>7.5</v>
-      </c>
-      <c r="C88" t="s">
-        <v>32</v>
       </c>
       <c r="D88" t="s">
         <v>535</v>
@@ -8546,11 +8546,11 @@
       <c r="A89" t="s">
         <v>150</v>
       </c>
-      <c r="B89">
+      <c r="B89" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C89" t="s">
-        <v>27</v>
       </c>
       <c r="D89" t="s">
         <v>538</v>
@@ -8601,11 +8601,11 @@
       <c r="A90" t="s">
         <v>151</v>
       </c>
-      <c r="B90">
+      <c r="B90" t="s">
+        <v>27</v>
+      </c>
+      <c r="C90">
         <v>8.9</v>
-      </c>
-      <c r="C90" t="s">
-        <v>27</v>
       </c>
       <c r="D90" t="s">
         <v>541</v>
@@ -8659,11 +8659,11 @@
       <c r="A91" t="s">
         <v>152</v>
       </c>
-      <c r="B91">
+      <c r="B91" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91">
         <v>8.1999999999999993</v>
-      </c>
-      <c r="C91" t="s">
-        <v>23</v>
       </c>
       <c r="D91" t="s">
         <v>543</v>
@@ -8714,11 +8714,11 @@
       <c r="A92" t="s">
         <v>153</v>
       </c>
-      <c r="B92">
+      <c r="B92" t="s">
+        <v>27</v>
+      </c>
+      <c r="C92">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C92" t="s">
-        <v>27</v>
       </c>
       <c r="D92" t="s">
         <v>546</v>
@@ -8769,7 +8769,7 @@
       <c r="A93" t="s">
         <v>154</v>
       </c>
-      <c r="B93">
+      <c r="C93">
         <v>7.2</v>
       </c>
       <c r="D93" t="s">
@@ -8821,11 +8821,11 @@
       <c r="A94" t="s">
         <v>155</v>
       </c>
-      <c r="B94">
+      <c r="B94" t="s">
+        <v>27</v>
+      </c>
+      <c r="C94">
         <v>8.4</v>
-      </c>
-      <c r="C94" t="s">
-        <v>27</v>
       </c>
       <c r="D94" t="s">
         <v>551</v>
@@ -8876,11 +8876,11 @@
       <c r="A95" t="s">
         <v>156</v>
       </c>
-      <c r="B95">
+      <c r="B95" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95">
         <v>8.9</v>
-      </c>
-      <c r="C95" t="s">
-        <v>27</v>
       </c>
       <c r="D95" t="s">
         <v>554</v>
@@ -8934,11 +8934,11 @@
       <c r="A96" t="s">
         <v>157</v>
       </c>
-      <c r="B96">
+      <c r="B96" t="s">
+        <v>27</v>
+      </c>
+      <c r="C96">
         <v>9.1999999999999993</v>
-      </c>
-      <c r="C96" t="s">
-        <v>27</v>
       </c>
       <c r="D96" t="s">
         <v>556</v>
@@ -8992,11 +8992,11 @@
       <c r="A97" t="s">
         <v>158</v>
       </c>
-      <c r="B97">
+      <c r="B97" t="s">
+        <v>27</v>
+      </c>
+      <c r="C97">
         <v>8.9</v>
-      </c>
-      <c r="C97" t="s">
-        <v>27</v>
       </c>
       <c r="D97" t="s">
         <v>559</v>
@@ -9050,11 +9050,11 @@
       <c r="A98" t="s">
         <v>159</v>
       </c>
-      <c r="B98">
+      <c r="B98" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98">
         <v>9.3000000000000007</v>
-      </c>
-      <c r="C98" t="s">
-        <v>27</v>
       </c>
       <c r="D98" t="s">
         <v>562</v>
@@ -9108,11 +9108,11 @@
       <c r="A99" t="s">
         <v>160</v>
       </c>
-      <c r="B99">
+      <c r="B99" t="s">
+        <v>27</v>
+      </c>
+      <c r="C99">
         <v>8.5</v>
-      </c>
-      <c r="C99" t="s">
-        <v>27</v>
       </c>
       <c r="D99" t="s">
         <v>565</v>
@@ -9166,11 +9166,11 @@
       <c r="A100" t="s">
         <v>161</v>
       </c>
-      <c r="B100">
+      <c r="B100" t="s">
+        <v>23</v>
+      </c>
+      <c r="C100">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C100" t="s">
-        <v>23</v>
       </c>
       <c r="D100" t="s">
         <v>567</v>
@@ -9221,11 +9221,11 @@
       <c r="A101" t="s">
         <v>162</v>
       </c>
-      <c r="B101">
+      <c r="B101" t="s">
+        <v>27</v>
+      </c>
+      <c r="C101">
         <v>8.9</v>
-      </c>
-      <c r="C101" t="s">
-        <v>27</v>
       </c>
       <c r="D101" t="s">
         <v>570</v>
@@ -9279,11 +9279,11 @@
       <c r="A102" t="s">
         <v>163</v>
       </c>
-      <c r="B102">
+      <c r="B102" t="s">
+        <v>27</v>
+      </c>
+      <c r="C102">
         <v>9.4</v>
-      </c>
-      <c r="C102" t="s">
-        <v>27</v>
       </c>
       <c r="D102" t="s">
         <v>573</v>
@@ -9337,11 +9337,11 @@
       <c r="A103" t="s">
         <v>164</v>
       </c>
-      <c r="B103">
+      <c r="B103" t="s">
+        <v>27</v>
+      </c>
+      <c r="C103">
         <v>8.9</v>
-      </c>
-      <c r="C103" t="s">
-        <v>27</v>
       </c>
       <c r="D103" t="s">
         <v>45</v>
@@ -9392,11 +9392,11 @@
       <c r="A104" t="s">
         <v>165</v>
       </c>
-      <c r="B104">
+      <c r="B104" t="s">
+        <v>27</v>
+      </c>
+      <c r="C104">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C104" t="s">
-        <v>27</v>
       </c>
       <c r="D104" t="s">
         <v>577</v>
@@ -9447,11 +9447,11 @@
       <c r="A105" t="s">
         <v>166</v>
       </c>
-      <c r="B105">
+      <c r="B105" t="s">
+        <v>27</v>
+      </c>
+      <c r="C105">
         <v>8.5</v>
-      </c>
-      <c r="C105" t="s">
-        <v>27</v>
       </c>
       <c r="D105" t="s">
         <v>580</v>
@@ -9505,11 +9505,11 @@
       <c r="A106" t="s">
         <v>167</v>
       </c>
-      <c r="B106">
+      <c r="B106" t="s">
+        <v>27</v>
+      </c>
+      <c r="C106">
         <v>8.6</v>
-      </c>
-      <c r="C106" t="s">
-        <v>27</v>
       </c>
       <c r="D106" t="s">
         <v>583</v>
@@ -9560,11 +9560,11 @@
       <c r="A107" t="s">
         <v>168</v>
       </c>
-      <c r="B107">
+      <c r="B107" t="s">
+        <v>23</v>
+      </c>
+      <c r="C107">
         <v>8.4</v>
-      </c>
-      <c r="C107" t="s">
-        <v>23</v>
       </c>
       <c r="D107" t="s">
         <v>586</v>
@@ -9618,11 +9618,11 @@
       <c r="A108" t="s">
         <v>169</v>
       </c>
-      <c r="B108">
+      <c r="B108" t="s">
+        <v>27</v>
+      </c>
+      <c r="C108">
         <v>9.3000000000000007</v>
-      </c>
-      <c r="C108" t="s">
-        <v>27</v>
       </c>
       <c r="D108" t="s">
         <v>589</v>
@@ -9676,11 +9676,11 @@
       <c r="A109" t="s">
         <v>170</v>
       </c>
-      <c r="B109">
+      <c r="B109" t="s">
+        <v>27</v>
+      </c>
+      <c r="C109">
         <v>9.3000000000000007</v>
-      </c>
-      <c r="C109" t="s">
-        <v>27</v>
       </c>
       <c r="D109" t="s">
         <v>592</v>
@@ -9731,11 +9731,11 @@
       <c r="A110" t="s">
         <v>171</v>
       </c>
-      <c r="B110">
+      <c r="B110" t="s">
+        <v>27</v>
+      </c>
+      <c r="C110">
         <v>8.6</v>
-      </c>
-      <c r="C110" t="s">
-        <v>27</v>
       </c>
       <c r="D110" t="s">
         <v>594</v>
@@ -9786,11 +9786,11 @@
       <c r="A111" t="s">
         <v>172</v>
       </c>
-      <c r="B111">
+      <c r="B111" t="s">
+        <v>27</v>
+      </c>
+      <c r="C111">
         <v>9.5</v>
-      </c>
-      <c r="C111" t="s">
-        <v>27</v>
       </c>
       <c r="D111" t="s">
         <v>597</v>
@@ -9844,11 +9844,11 @@
       <c r="A112" t="s">
         <v>173</v>
       </c>
-      <c r="B112">
+      <c r="B112" t="s">
+        <v>27</v>
+      </c>
+      <c r="C112">
         <v>9.1</v>
-      </c>
-      <c r="C112" t="s">
-        <v>27</v>
       </c>
       <c r="D112" t="s">
         <v>599</v>
@@ -9902,7 +9902,7 @@
       <c r="A113" t="s">
         <v>174</v>
       </c>
-      <c r="B113">
+      <c r="C113">
         <v>7.3</v>
       </c>
       <c r="D113" t="s">
@@ -9954,11 +9954,11 @@
       <c r="A114" t="s">
         <v>175</v>
       </c>
-      <c r="B114">
+      <c r="B114" t="s">
+        <v>27</v>
+      </c>
+      <c r="C114">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C114" t="s">
-        <v>27</v>
       </c>
       <c r="D114" t="s">
         <v>604</v>
@@ -10012,11 +10012,11 @@
       <c r="A115" t="s">
         <v>176</v>
       </c>
-      <c r="B115">
+      <c r="B115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C115">
         <v>8.6</v>
-      </c>
-      <c r="C115" t="s">
-        <v>27</v>
       </c>
       <c r="D115" t="s">
         <v>606</v>
@@ -10067,11 +10067,11 @@
       <c r="A116" t="s">
         <v>177</v>
       </c>
-      <c r="B116">
+      <c r="B116" t="s">
+        <v>27</v>
+      </c>
+      <c r="C116">
         <v>8.6</v>
-      </c>
-      <c r="C116" t="s">
-        <v>27</v>
       </c>
       <c r="D116" t="s">
         <v>609</v>
@@ -10122,11 +10122,11 @@
       <c r="A117" t="s">
         <v>178</v>
       </c>
-      <c r="B117">
+      <c r="B117" t="s">
+        <v>27</v>
+      </c>
+      <c r="C117">
         <v>8.9</v>
-      </c>
-      <c r="C117" t="s">
-        <v>27</v>
       </c>
       <c r="D117" t="s">
         <v>611</v>
@@ -10180,11 +10180,11 @@
       <c r="A118" t="s">
         <v>179</v>
       </c>
-      <c r="B118">
+      <c r="B118" t="s">
+        <v>27</v>
+      </c>
+      <c r="C118">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C118" t="s">
-        <v>27</v>
       </c>
       <c r="D118" t="s">
         <v>613</v>
@@ -10238,11 +10238,11 @@
       <c r="A119" t="s">
         <v>180</v>
       </c>
-      <c r="B119">
+      <c r="B119" t="s">
+        <v>27</v>
+      </c>
+      <c r="C119">
         <v>8.5</v>
-      </c>
-      <c r="C119" t="s">
-        <v>27</v>
       </c>
       <c r="D119" t="s">
         <v>616</v>
@@ -10296,11 +10296,11 @@
       <c r="A120" t="s">
         <v>181</v>
       </c>
-      <c r="B120">
+      <c r="B120" t="s">
+        <v>23</v>
+      </c>
+      <c r="C120">
         <v>8.4</v>
-      </c>
-      <c r="C120" t="s">
-        <v>23</v>
       </c>
       <c r="D120" t="s">
         <v>618</v>
@@ -10354,11 +10354,11 @@
       <c r="A121" t="s">
         <v>182</v>
       </c>
-      <c r="B121">
+      <c r="B121" t="s">
+        <v>27</v>
+      </c>
+      <c r="C121">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C121" t="s">
-        <v>27</v>
       </c>
       <c r="D121" t="s">
         <v>621</v>
@@ -10412,11 +10412,11 @@
       <c r="A122" t="s">
         <v>183</v>
       </c>
-      <c r="B122">
+      <c r="B122" t="s">
+        <v>27</v>
+      </c>
+      <c r="C122">
         <v>8.5</v>
-      </c>
-      <c r="C122" t="s">
-        <v>27</v>
       </c>
       <c r="D122" t="s">
         <v>624</v>
@@ -10470,11 +10470,11 @@
       <c r="A123" t="s">
         <v>184</v>
       </c>
-      <c r="B123">
+      <c r="B123" t="s">
+        <v>27</v>
+      </c>
+      <c r="C123">
         <v>8.6</v>
-      </c>
-      <c r="C123" t="s">
-        <v>27</v>
       </c>
       <c r="D123" t="s">
         <v>627</v>
@@ -10525,11 +10525,11 @@
       <c r="A124" t="s">
         <v>185</v>
       </c>
-      <c r="B124">
+      <c r="B124" t="s">
+        <v>23</v>
+      </c>
+      <c r="C124">
         <v>8.1999999999999993</v>
-      </c>
-      <c r="C124" t="s">
-        <v>23</v>
       </c>
       <c r="D124" t="s">
         <v>629</v>
@@ -10580,11 +10580,11 @@
       <c r="A125" t="s">
         <v>186</v>
       </c>
-      <c r="B125">
+      <c r="B125" t="s">
+        <v>27</v>
+      </c>
+      <c r="C125">
         <v>8.9</v>
-      </c>
-      <c r="C125" t="s">
-        <v>27</v>
       </c>
       <c r="D125" t="s">
         <v>633</v>
@@ -10635,11 +10635,11 @@
       <c r="A126" t="s">
         <v>187</v>
       </c>
-      <c r="B126">
+      <c r="B126" t="s">
+        <v>27</v>
+      </c>
+      <c r="C126">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C126" t="s">
-        <v>27</v>
       </c>
       <c r="D126" t="s">
         <v>635</v>
@@ -10690,11 +10690,11 @@
       <c r="A127" t="s">
         <v>188</v>
       </c>
-      <c r="B127">
+      <c r="B127" t="s">
+        <v>23</v>
+      </c>
+      <c r="C127">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C127" t="s">
-        <v>23</v>
       </c>
       <c r="D127" t="s">
         <v>637</v>
@@ -10745,11 +10745,11 @@
       <c r="A128" t="s">
         <v>189</v>
       </c>
-      <c r="B128">
+      <c r="B128" t="s">
+        <v>27</v>
+      </c>
+      <c r="C128">
         <v>9.1999999999999993</v>
-      </c>
-      <c r="C128" t="s">
-        <v>27</v>
       </c>
       <c r="D128" t="s">
         <v>601</v>
@@ -10803,7 +10803,7 @@
       <c r="A129" t="s">
         <v>190</v>
       </c>
-      <c r="B129">
+      <c r="C129">
         <v>7.3</v>
       </c>
       <c r="D129" t="s">
@@ -10855,11 +10855,11 @@
       <c r="A130" t="s">
         <v>191</v>
       </c>
-      <c r="B130">
+      <c r="B130" t="s">
+        <v>32</v>
+      </c>
+      <c r="C130">
         <v>7.8</v>
-      </c>
-      <c r="C130" t="s">
-        <v>32</v>
       </c>
       <c r="D130" t="s">
         <v>643</v>
@@ -10910,11 +10910,11 @@
       <c r="A131" t="s">
         <v>192</v>
       </c>
-      <c r="B131">
+      <c r="B131" t="s">
+        <v>23</v>
+      </c>
+      <c r="C131">
         <v>8</v>
-      </c>
-      <c r="C131" t="s">
-        <v>23</v>
       </c>
       <c r="D131" t="s">
         <v>645</v>
@@ -10968,11 +10968,11 @@
       <c r="A132" t="s">
         <v>193</v>
       </c>
-      <c r="B132">
+      <c r="B132" t="s">
+        <v>32</v>
+      </c>
+      <c r="C132">
         <v>7.9</v>
-      </c>
-      <c r="C132" t="s">
-        <v>32</v>
       </c>
       <c r="D132" t="s">
         <v>647</v>
@@ -11023,11 +11023,11 @@
       <c r="A133" t="s">
         <v>194</v>
       </c>
-      <c r="B133">
+      <c r="B133" t="s">
+        <v>32</v>
+      </c>
+      <c r="C133">
         <v>7.7</v>
-      </c>
-      <c r="C133" t="s">
-        <v>32</v>
       </c>
       <c r="D133" t="s">
         <v>649</v>
@@ -11081,11 +11081,11 @@
       <c r="A134" t="s">
         <v>195</v>
       </c>
-      <c r="B134">
+      <c r="B134" t="s">
+        <v>32</v>
+      </c>
+      <c r="C134">
         <v>7.7</v>
-      </c>
-      <c r="C134" t="s">
-        <v>32</v>
       </c>
       <c r="D134" t="s">
         <v>651</v>
@@ -11136,7 +11136,7 @@
       <c r="A135" t="s">
         <v>196</v>
       </c>
-      <c r="B135">
+      <c r="C135">
         <v>7.2</v>
       </c>
       <c r="D135" t="s">
@@ -11188,7 +11188,7 @@
       <c r="A136" t="s">
         <v>197</v>
       </c>
-      <c r="B136">
+      <c r="C136">
         <v>7.4</v>
       </c>
       <c r="D136" t="s">
@@ -11240,11 +11240,11 @@
       <c r="A137" t="s">
         <v>198</v>
       </c>
-      <c r="B137">
+      <c r="B137" t="s">
+        <v>27</v>
+      </c>
+      <c r="C137">
         <v>9</v>
-      </c>
-      <c r="C137" t="s">
-        <v>27</v>
       </c>
       <c r="D137" t="s">
         <v>657</v>
@@ -11298,11 +11298,11 @@
       <c r="A138" t="s">
         <v>199</v>
       </c>
-      <c r="B138">
+      <c r="B138" t="s">
+        <v>32</v>
+      </c>
+      <c r="C138">
         <v>7.5</v>
-      </c>
-      <c r="C138" t="s">
-        <v>32</v>
       </c>
       <c r="D138" t="s">
         <v>659</v>
@@ -11356,11 +11356,11 @@
       <c r="A139" t="s">
         <v>200</v>
       </c>
-      <c r="B139">
+      <c r="B139" t="s">
+        <v>27</v>
+      </c>
+      <c r="C139">
         <v>9.1</v>
-      </c>
-      <c r="C139" t="s">
-        <v>27</v>
       </c>
       <c r="D139" t="s">
         <v>661</v>
@@ -11411,11 +11411,11 @@
       <c r="A140" t="s">
         <v>201</v>
       </c>
-      <c r="B140">
+      <c r="B140" t="s">
+        <v>23</v>
+      </c>
+      <c r="C140">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C140" t="s">
-        <v>23</v>
       </c>
       <c r="D140" t="s">
         <v>664</v>
@@ -11466,11 +11466,11 @@
       <c r="A141" t="s">
         <v>202</v>
       </c>
-      <c r="B141">
+      <c r="B141" t="s">
+        <v>27</v>
+      </c>
+      <c r="C141">
         <v>8.9</v>
-      </c>
-      <c r="C141" t="s">
-        <v>27</v>
       </c>
       <c r="D141" t="s">
         <v>666</v>
@@ -11521,11 +11521,11 @@
       <c r="A142" t="s">
         <v>203</v>
       </c>
-      <c r="B142">
+      <c r="B142" t="s">
+        <v>27</v>
+      </c>
+      <c r="C142">
         <v>8.5</v>
-      </c>
-      <c r="C142" t="s">
-        <v>27</v>
       </c>
       <c r="D142" t="s">
         <v>668</v>
@@ -11576,11 +11576,11 @@
       <c r="A143" t="s">
         <v>204</v>
       </c>
-      <c r="B143">
+      <c r="B143" t="s">
+        <v>27</v>
+      </c>
+      <c r="C143">
         <v>8.5</v>
-      </c>
-      <c r="C143" t="s">
-        <v>27</v>
       </c>
       <c r="D143" t="s">
         <v>38</v>
@@ -11634,7 +11634,7 @@
       <c r="A144" t="s">
         <v>205</v>
       </c>
-      <c r="B144">
+      <c r="C144">
         <v>6.6</v>
       </c>
       <c r="D144" t="s">
@@ -11689,11 +11689,11 @@
       <c r="A145" t="s">
         <v>206</v>
       </c>
-      <c r="B145">
+      <c r="B145" t="s">
+        <v>32</v>
+      </c>
+      <c r="C145">
         <v>7.8</v>
-      </c>
-      <c r="C145" t="s">
-        <v>32</v>
       </c>
       <c r="D145" t="s">
         <v>673</v>
@@ -11744,11 +11744,11 @@
       <c r="A146" t="s">
         <v>207</v>
       </c>
-      <c r="B146">
+      <c r="B146" t="s">
+        <v>27</v>
+      </c>
+      <c r="C146">
         <v>8.5</v>
-      </c>
-      <c r="C146" t="s">
-        <v>27</v>
       </c>
       <c r="D146" t="s">
         <v>675</v>
@@ -11802,11 +11802,11 @@
       <c r="A147" t="s">
         <v>208</v>
       </c>
-      <c r="B147">
+      <c r="B147" t="s">
+        <v>27</v>
+      </c>
+      <c r="C147">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C147" t="s">
-        <v>27</v>
       </c>
       <c r="D147" t="s">
         <v>677</v>
@@ -11857,11 +11857,11 @@
       <c r="A148" t="s">
         <v>209</v>
       </c>
-      <c r="B148">
+      <c r="B148" t="s">
+        <v>27</v>
+      </c>
+      <c r="C148">
         <v>9.3000000000000007</v>
-      </c>
-      <c r="C148" t="s">
-        <v>27</v>
       </c>
       <c r="D148" t="s">
         <v>679</v>
@@ -11915,11 +11915,11 @@
       <c r="A149" t="s">
         <v>210</v>
       </c>
-      <c r="B149">
+      <c r="B149" t="s">
+        <v>27</v>
+      </c>
+      <c r="C149">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C149" t="s">
-        <v>27</v>
       </c>
       <c r="D149" t="s">
         <v>682</v>
@@ -11970,11 +11970,11 @@
       <c r="A150" t="s">
         <v>211</v>
       </c>
-      <c r="B150">
+      <c r="B150" t="s">
+        <v>27</v>
+      </c>
+      <c r="C150">
         <v>8.6</v>
-      </c>
-      <c r="C150" t="s">
-        <v>27</v>
       </c>
       <c r="D150" t="s">
         <v>685</v>
@@ -12025,11 +12025,11 @@
       <c r="A151" t="s">
         <v>212</v>
       </c>
-      <c r="B151">
+      <c r="B151" t="s">
+        <v>27</v>
+      </c>
+      <c r="C151">
         <v>9</v>
-      </c>
-      <c r="C151" t="s">
-        <v>27</v>
       </c>
       <c r="D151" t="s">
         <v>687</v>
@@ -12083,11 +12083,11 @@
       <c r="A152" t="s">
         <v>213</v>
       </c>
-      <c r="B152">
+      <c r="B152" t="s">
+        <v>23</v>
+      </c>
+      <c r="C152">
         <v>8.1999999999999993</v>
-      </c>
-      <c r="C152" t="s">
-        <v>23</v>
       </c>
       <c r="D152" t="s">
         <v>689</v>
@@ -12138,11 +12138,11 @@
       <c r="A153" t="s">
         <v>214</v>
       </c>
-      <c r="B153">
+      <c r="B153" t="s">
+        <v>27</v>
+      </c>
+      <c r="C153">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C153" t="s">
-        <v>27</v>
       </c>
       <c r="D153" t="s">
         <v>693</v>
@@ -12196,11 +12196,11 @@
       <c r="A154" t="s">
         <v>215</v>
       </c>
-      <c r="B154">
+      <c r="B154" t="s">
+        <v>27</v>
+      </c>
+      <c r="C154">
         <v>9.1</v>
-      </c>
-      <c r="C154" t="s">
-        <v>27</v>
       </c>
       <c r="D154" t="s">
         <v>696</v>
@@ -12254,11 +12254,11 @@
       <c r="A155" t="s">
         <v>216</v>
       </c>
-      <c r="B155">
+      <c r="B155" t="s">
+        <v>27</v>
+      </c>
+      <c r="C155">
         <v>8.9</v>
-      </c>
-      <c r="C155" t="s">
-        <v>27</v>
       </c>
       <c r="D155" t="s">
         <v>698</v>
@@ -12312,11 +12312,11 @@
       <c r="A156" t="s">
         <v>217</v>
       </c>
-      <c r="B156">
+      <c r="B156" t="s">
+        <v>23</v>
+      </c>
+      <c r="C156">
         <v>8.1999999999999993</v>
-      </c>
-      <c r="C156" t="s">
-        <v>23</v>
       </c>
       <c r="D156" t="s">
         <v>700</v>
@@ -12370,11 +12370,11 @@
       <c r="A157" t="s">
         <v>218</v>
       </c>
-      <c r="B157">
+      <c r="B157" t="s">
+        <v>27</v>
+      </c>
+      <c r="C157">
         <v>9</v>
-      </c>
-      <c r="C157" t="s">
-        <v>27</v>
       </c>
       <c r="D157" t="s">
         <v>48</v>
@@ -12428,11 +12428,11 @@
       <c r="A158" t="s">
         <v>219</v>
       </c>
-      <c r="B158">
+      <c r="B158" t="s">
+        <v>23</v>
+      </c>
+      <c r="C158">
         <v>8</v>
-      </c>
-      <c r="C158" t="s">
-        <v>23</v>
       </c>
       <c r="D158" t="s">
         <v>703</v>
@@ -12474,7 +12474,7 @@
       <c r="A159" t="s">
         <v>220</v>
       </c>
-      <c r="B159">
+      <c r="C159">
         <v>7.4</v>
       </c>
       <c r="D159" t="s">
@@ -12529,11 +12529,11 @@
       <c r="A160" t="s">
         <v>221</v>
       </c>
-      <c r="B160">
+      <c r="B160" t="s">
+        <v>27</v>
+      </c>
+      <c r="C160">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C160" t="s">
-        <v>27</v>
       </c>
       <c r="D160" t="s">
         <v>706</v>
@@ -12587,11 +12587,11 @@
       <c r="A161" t="s">
         <v>222</v>
       </c>
-      <c r="B161">
+      <c r="B161" t="s">
+        <v>27</v>
+      </c>
+      <c r="C161">
         <v>8.9</v>
-      </c>
-      <c r="C161" t="s">
-        <v>27</v>
       </c>
       <c r="D161" t="s">
         <v>709</v>
@@ -12642,11 +12642,11 @@
       <c r="A162" t="s">
         <v>223</v>
       </c>
-      <c r="B162">
+      <c r="B162" t="s">
+        <v>23</v>
+      </c>
+      <c r="C162">
         <v>7.9</v>
-      </c>
-      <c r="C162" t="s">
-        <v>23</v>
       </c>
       <c r="D162" t="s">
         <v>711</v>
@@ -12700,11 +12700,11 @@
       <c r="A163" t="s">
         <v>224</v>
       </c>
-      <c r="B163">
+      <c r="B163" t="s">
+        <v>27</v>
+      </c>
+      <c r="C163">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C163" t="s">
-        <v>27</v>
       </c>
       <c r="D163" t="s">
         <v>713</v>
@@ -12758,11 +12758,11 @@
       <c r="A164" t="s">
         <v>225</v>
       </c>
-      <c r="B164">
+      <c r="B164" t="s">
+        <v>27</v>
+      </c>
+      <c r="C164">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C164" t="s">
-        <v>27</v>
       </c>
       <c r="D164" t="s">
         <v>716</v>
@@ -12816,11 +12816,11 @@
       <c r="A165" t="s">
         <v>226</v>
       </c>
-      <c r="B165">
+      <c r="B165" t="s">
+        <v>27</v>
+      </c>
+      <c r="C165">
         <v>9.1</v>
-      </c>
-      <c r="C165" t="s">
-        <v>27</v>
       </c>
       <c r="D165" t="s">
         <v>719</v>
@@ -12874,11 +12874,11 @@
       <c r="A166" t="s">
         <v>227</v>
       </c>
-      <c r="B166">
+      <c r="B166" t="s">
+        <v>27</v>
+      </c>
+      <c r="C166">
         <v>8.9</v>
-      </c>
-      <c r="C166" t="s">
-        <v>27</v>
       </c>
       <c r="D166" t="s">
         <v>722</v>
@@ -12929,11 +12929,11 @@
       <c r="A167" t="s">
         <v>228</v>
       </c>
-      <c r="B167">
+      <c r="B167" t="s">
+        <v>32</v>
+      </c>
+      <c r="C167">
         <v>7.7</v>
-      </c>
-      <c r="C167" t="s">
-        <v>32</v>
       </c>
       <c r="D167" t="s">
         <v>724</v>
@@ -12987,11 +12987,11 @@
       <c r="A168" t="s">
         <v>229</v>
       </c>
-      <c r="B168">
+      <c r="B168" t="s">
+        <v>27</v>
+      </c>
+      <c r="C168">
         <v>9.1</v>
-      </c>
-      <c r="C168" t="s">
-        <v>27</v>
       </c>
       <c r="D168" t="s">
         <v>727</v>
@@ -13042,11 +13042,11 @@
       <c r="A169" t="s">
         <v>230</v>
       </c>
-      <c r="B169">
+      <c r="B169" t="s">
+        <v>27</v>
+      </c>
+      <c r="C169">
         <v>9.3000000000000007</v>
-      </c>
-      <c r="C169" t="s">
-        <v>27</v>
       </c>
       <c r="D169" t="s">
         <v>730</v>
@@ -13100,11 +13100,11 @@
       <c r="A170" t="s">
         <v>231</v>
       </c>
-      <c r="B170">
+      <c r="B170" t="s">
+        <v>27</v>
+      </c>
+      <c r="C170">
         <v>8.5</v>
-      </c>
-      <c r="C170" t="s">
-        <v>27</v>
       </c>
       <c r="D170" t="s">
         <v>732</v>
@@ -13155,11 +13155,11 @@
       <c r="A171" t="s">
         <v>232</v>
       </c>
-      <c r="B171">
+      <c r="B171" t="s">
+        <v>27</v>
+      </c>
+      <c r="C171">
         <v>9.1</v>
-      </c>
-      <c r="C171" t="s">
-        <v>27</v>
       </c>
       <c r="D171" t="s">
         <v>734</v>
@@ -13210,11 +13210,11 @@
       <c r="A172" t="s">
         <v>233</v>
       </c>
-      <c r="B172">
+      <c r="B172" t="s">
+        <v>27</v>
+      </c>
+      <c r="C172">
         <v>8.6</v>
-      </c>
-      <c r="C172" t="s">
-        <v>27</v>
       </c>
       <c r="D172" t="s">
         <v>736</v>
@@ -13265,11 +13265,11 @@
       <c r="A173" t="s">
         <v>234</v>
       </c>
-      <c r="B173">
+      <c r="B173" t="s">
+        <v>27</v>
+      </c>
+      <c r="C173">
         <v>9.1</v>
-      </c>
-      <c r="C173" t="s">
-        <v>27</v>
       </c>
       <c r="D173" t="s">
         <v>739</v>
@@ -13323,7 +13323,7 @@
       <c r="A174" t="s">
         <v>235</v>
       </c>
-      <c r="B174">
+      <c r="C174">
         <v>7.3</v>
       </c>
       <c r="D174" t="s">
@@ -13378,11 +13378,11 @@
       <c r="A175" t="s">
         <v>236</v>
       </c>
-      <c r="B175">
+      <c r="B175" t="s">
+        <v>27</v>
+      </c>
+      <c r="C175">
         <v>8.9</v>
-      </c>
-      <c r="C175" t="s">
-        <v>27</v>
       </c>
       <c r="D175" t="s">
         <v>742</v>
@@ -13433,11 +13433,11 @@
       <c r="A176" t="s">
         <v>237</v>
       </c>
-      <c r="B176">
+      <c r="B176" t="s">
+        <v>27</v>
+      </c>
+      <c r="C176">
         <v>8.9</v>
-      </c>
-      <c r="C176" t="s">
-        <v>27</v>
       </c>
       <c r="D176" t="s">
         <v>745</v>
@@ -13488,11 +13488,11 @@
       <c r="A177" t="s">
         <v>238</v>
       </c>
-      <c r="B177">
+      <c r="B177" t="s">
+        <v>23</v>
+      </c>
+      <c r="C177">
         <v>8</v>
-      </c>
-      <c r="C177" t="s">
-        <v>23</v>
       </c>
       <c r="D177" t="s">
         <v>748</v>
@@ -13546,11 +13546,11 @@
       <c r="A178" t="s">
         <v>239</v>
       </c>
-      <c r="B178">
+      <c r="B178" t="s">
+        <v>27</v>
+      </c>
+      <c r="C178">
         <v>9.1</v>
-      </c>
-      <c r="C178" t="s">
-        <v>27</v>
       </c>
       <c r="D178" t="s">
         <v>750</v>
@@ -13604,11 +13604,11 @@
       <c r="A179" t="s">
         <v>240</v>
       </c>
-      <c r="B179">
+      <c r="B179" t="s">
+        <v>27</v>
+      </c>
+      <c r="C179">
         <v>9.1</v>
-      </c>
-      <c r="C179" t="s">
-        <v>27</v>
       </c>
       <c r="D179" t="s">
         <v>753</v>
@@ -13662,11 +13662,11 @@
       <c r="A180" t="s">
         <v>241</v>
       </c>
-      <c r="B180">
+      <c r="B180" t="s">
+        <v>27</v>
+      </c>
+      <c r="C180">
         <v>9.3000000000000007</v>
-      </c>
-      <c r="C180" t="s">
-        <v>27</v>
       </c>
       <c r="D180" t="s">
         <v>436</v>
@@ -13720,11 +13720,11 @@
       <c r="A181" t="s">
         <v>242</v>
       </c>
-      <c r="B181">
+      <c r="B181" t="s">
+        <v>23</v>
+      </c>
+      <c r="C181">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C181" t="s">
-        <v>23</v>
       </c>
       <c r="D181" t="s">
         <v>758</v>
@@ -13775,11 +13775,11 @@
       <c r="A182" t="s">
         <v>243</v>
       </c>
-      <c r="B182">
+      <c r="B182" t="s">
+        <v>27</v>
+      </c>
+      <c r="C182">
         <v>9</v>
-      </c>
-      <c r="C182" t="s">
-        <v>27</v>
       </c>
       <c r="D182" t="s">
         <v>761</v>
@@ -13833,11 +13833,11 @@
       <c r="A183" t="s">
         <v>244</v>
       </c>
-      <c r="B183">
+      <c r="B183" t="s">
+        <v>23</v>
+      </c>
+      <c r="C183">
         <v>8.4</v>
-      </c>
-      <c r="C183" t="s">
-        <v>23</v>
       </c>
       <c r="D183" t="s">
         <v>764</v>
@@ -13891,11 +13891,11 @@
       <c r="A184" t="s">
         <v>245</v>
       </c>
-      <c r="B184">
+      <c r="B184" t="s">
+        <v>23</v>
+      </c>
+      <c r="C184">
         <v>8</v>
-      </c>
-      <c r="C184" t="s">
-        <v>23</v>
       </c>
       <c r="D184" t="s">
         <v>767</v>
@@ -13946,7 +13946,7 @@
       <c r="A185" t="s">
         <v>246</v>
       </c>
-      <c r="B185">
+      <c r="C185">
         <v>7.2</v>
       </c>
       <c r="D185" t="s">
@@ -13998,11 +13998,11 @@
       <c r="A186" t="s">
         <v>247</v>
       </c>
-      <c r="B186">
+      <c r="B186" t="s">
+        <v>27</v>
+      </c>
+      <c r="C186">
         <v>9.1</v>
-      </c>
-      <c r="C186" t="s">
-        <v>27</v>
       </c>
       <c r="D186" t="s">
         <v>772</v>
@@ -14056,11 +14056,11 @@
       <c r="A187" t="s">
         <v>248</v>
       </c>
-      <c r="B187">
+      <c r="B187" t="s">
+        <v>27</v>
+      </c>
+      <c r="C187">
         <v>8.9</v>
-      </c>
-      <c r="C187" t="s">
-        <v>27</v>
       </c>
       <c r="D187" t="s">
         <v>774</v>
@@ -14114,11 +14114,11 @@
       <c r="A188" t="s">
         <v>249</v>
       </c>
-      <c r="B188">
+      <c r="B188" t="s">
+        <v>27</v>
+      </c>
+      <c r="C188">
         <v>8.4</v>
-      </c>
-      <c r="C188" t="s">
-        <v>27</v>
       </c>
       <c r="D188" t="s">
         <v>776</v>
@@ -14169,11 +14169,11 @@
       <c r="A189" t="s">
         <v>250</v>
       </c>
-      <c r="B189">
+      <c r="B189" t="s">
+        <v>27</v>
+      </c>
+      <c r="C189">
         <v>8.9</v>
-      </c>
-      <c r="C189" t="s">
-        <v>27</v>
       </c>
       <c r="D189" t="s">
         <v>778</v>
@@ -14224,11 +14224,11 @@
       <c r="A190" t="s">
         <v>251</v>
       </c>
-      <c r="B190">
+      <c r="B190" t="s">
+        <v>27</v>
+      </c>
+      <c r="C190">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C190" t="s">
-        <v>27</v>
       </c>
       <c r="D190" t="s">
         <v>780</v>
@@ -14282,11 +14282,11 @@
       <c r="A191" t="s">
         <v>252</v>
       </c>
-      <c r="B191">
+      <c r="B191" t="s">
+        <v>27</v>
+      </c>
+      <c r="C191">
         <v>8.6</v>
-      </c>
-      <c r="C191" t="s">
-        <v>27</v>
       </c>
       <c r="D191" t="s">
         <v>782</v>
@@ -14337,11 +14337,11 @@
       <c r="A192" t="s">
         <v>253</v>
       </c>
-      <c r="B192">
+      <c r="B192" t="s">
+        <v>27</v>
+      </c>
+      <c r="C192">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C192" t="s">
-        <v>27</v>
       </c>
       <c r="D192" t="s">
         <v>784</v>
@@ -14392,11 +14392,11 @@
       <c r="A193" t="s">
         <v>254</v>
       </c>
-      <c r="B193">
+      <c r="B193" t="s">
+        <v>27</v>
+      </c>
+      <c r="C193">
         <v>8.5</v>
-      </c>
-      <c r="C193" t="s">
-        <v>27</v>
       </c>
       <c r="D193" t="s">
         <v>787</v>
@@ -14450,11 +14450,11 @@
       <c r="A194" t="s">
         <v>255</v>
       </c>
-      <c r="B194">
+      <c r="B194" t="s">
+        <v>27</v>
+      </c>
+      <c r="C194">
         <v>9.5</v>
-      </c>
-      <c r="C194" t="s">
-        <v>27</v>
       </c>
       <c r="D194" t="s">
         <v>790</v>
@@ -14508,11 +14508,11 @@
       <c r="A195" t="s">
         <v>256</v>
       </c>
-      <c r="B195">
+      <c r="B195" t="s">
+        <v>27</v>
+      </c>
+      <c r="C195">
         <v>9.5</v>
-      </c>
-      <c r="C195" t="s">
-        <v>27</v>
       </c>
       <c r="D195" t="s">
         <v>792</v>
@@ -14566,11 +14566,11 @@
       <c r="A196" t="s">
         <v>257</v>
       </c>
-      <c r="B196">
+      <c r="B196" t="s">
+        <v>27</v>
+      </c>
+      <c r="C196">
         <v>9.4</v>
-      </c>
-      <c r="C196" t="s">
-        <v>27</v>
       </c>
       <c r="D196" t="s">
         <v>795</v>
@@ -14624,11 +14624,11 @@
       <c r="A197" t="s">
         <v>258</v>
       </c>
-      <c r="B197">
+      <c r="B197" t="s">
+        <v>27</v>
+      </c>
+      <c r="C197">
         <v>9.5</v>
-      </c>
-      <c r="C197" t="s">
-        <v>27</v>
       </c>
       <c r="D197" t="s">
         <v>797</v>
@@ -14682,11 +14682,11 @@
       <c r="A198" t="s">
         <v>259</v>
       </c>
-      <c r="B198">
+      <c r="B198" t="s">
+        <v>27</v>
+      </c>
+      <c r="C198">
         <v>9.4</v>
-      </c>
-      <c r="C198" t="s">
-        <v>27</v>
       </c>
       <c r="D198" t="s">
         <v>799</v>
@@ -14740,11 +14740,11 @@
       <c r="A199" t="s">
         <v>260</v>
       </c>
-      <c r="B199">
+      <c r="B199" t="s">
+        <v>27</v>
+      </c>
+      <c r="C199">
         <v>9.4</v>
-      </c>
-      <c r="C199" t="s">
-        <v>27</v>
       </c>
       <c r="D199" t="s">
         <v>801</v>
@@ -14798,11 +14798,11 @@
       <c r="A200" t="s">
         <v>261</v>
       </c>
-      <c r="B200">
+      <c r="B200" t="s">
+        <v>23</v>
+      </c>
+      <c r="C200">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C200" t="s">
-        <v>23</v>
       </c>
       <c r="D200" t="s">
         <v>804</v>
@@ -14853,11 +14853,11 @@
       <c r="A201" t="s">
         <v>262</v>
       </c>
-      <c r="B201">
+      <c r="B201" t="s">
+        <v>27</v>
+      </c>
+      <c r="C201">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C201" t="s">
-        <v>27</v>
       </c>
       <c r="D201" t="s">
         <v>806</v>
@@ -14911,11 +14911,11 @@
       <c r="A202" t="s">
         <v>263</v>
       </c>
-      <c r="B202">
+      <c r="B202" t="s">
+        <v>27</v>
+      </c>
+      <c r="C202">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C202" t="s">
-        <v>27</v>
       </c>
       <c r="D202" t="s">
         <v>808</v>
@@ -14969,11 +14969,11 @@
       <c r="A203" t="s">
         <v>264</v>
       </c>
-      <c r="B203">
+      <c r="B203" t="s">
+        <v>27</v>
+      </c>
+      <c r="C203">
         <v>9.1</v>
-      </c>
-      <c r="C203" t="s">
-        <v>27</v>
       </c>
       <c r="D203" t="s">
         <v>810</v>
@@ -15024,7 +15024,7 @@
       <c r="A204" t="s">
         <v>265</v>
       </c>
-      <c r="B204">
+      <c r="C204">
         <v>7.2</v>
       </c>
       <c r="D204" t="s">
@@ -15073,7 +15073,7 @@
       <c r="A205" t="s">
         <v>266</v>
       </c>
-      <c r="B205">
+      <c r="C205">
         <v>6.3</v>
       </c>
       <c r="D205" t="s">
@@ -15125,11 +15125,11 @@
       <c r="A206" t="s">
         <v>267</v>
       </c>
-      <c r="B206">
+      <c r="B206" t="s">
+        <v>23</v>
+      </c>
+      <c r="C206">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C206" t="s">
-        <v>23</v>
       </c>
       <c r="D206" t="s">
         <v>815</v>
@@ -15180,11 +15180,11 @@
       <c r="A207" t="s">
         <v>268</v>
       </c>
-      <c r="B207">
+      <c r="B207" t="s">
+        <v>27</v>
+      </c>
+      <c r="C207">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C207" t="s">
-        <v>27</v>
       </c>
       <c r="D207" t="s">
         <v>817</v>
@@ -15235,11 +15235,11 @@
       <c r="A208" t="s">
         <v>269</v>
       </c>
-      <c r="B208">
+      <c r="B208" t="s">
+        <v>27</v>
+      </c>
+      <c r="C208">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C208" t="s">
-        <v>27</v>
       </c>
       <c r="D208" t="s">
         <v>819</v>
@@ -15290,11 +15290,11 @@
       <c r="A209" t="s">
         <v>270</v>
       </c>
-      <c r="B209">
+      <c r="B209" t="s">
+        <v>27</v>
+      </c>
+      <c r="C209">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C209" t="s">
-        <v>27</v>
       </c>
       <c r="D209" t="s">
         <v>821</v>
@@ -15345,11 +15345,11 @@
       <c r="A210" t="s">
         <v>271</v>
       </c>
-      <c r="B210">
+      <c r="B210" t="s">
+        <v>27</v>
+      </c>
+      <c r="C210">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C210" t="s">
-        <v>27</v>
       </c>
       <c r="D210" t="s">
         <v>823</v>
@@ -15400,11 +15400,11 @@
       <c r="A211" t="s">
         <v>272</v>
       </c>
-      <c r="B211">
+      <c r="B211" t="s">
+        <v>27</v>
+      </c>
+      <c r="C211">
         <v>9</v>
-      </c>
-      <c r="C211" t="s">
-        <v>27</v>
       </c>
       <c r="D211" t="s">
         <v>825</v>
@@ -15458,11 +15458,11 @@
       <c r="A212" t="s">
         <v>273</v>
       </c>
-      <c r="B212">
+      <c r="B212" t="s">
+        <v>27</v>
+      </c>
+      <c r="C212">
         <v>9.1</v>
-      </c>
-      <c r="C212" t="s">
-        <v>27</v>
       </c>
       <c r="D212" t="s">
         <v>827</v>
@@ -15516,11 +15516,11 @@
       <c r="A213" t="s">
         <v>274</v>
       </c>
-      <c r="B213">
+      <c r="B213" t="s">
+        <v>27</v>
+      </c>
+      <c r="C213">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C213" t="s">
-        <v>27</v>
       </c>
       <c r="D213" t="s">
         <v>830</v>
@@ -15574,11 +15574,11 @@
       <c r="A214" t="s">
         <v>275</v>
       </c>
-      <c r="B214">
+      <c r="B214" t="s">
+        <v>23</v>
+      </c>
+      <c r="C214">
         <v>8.3000000000000007</v>
-      </c>
-      <c r="C214" t="s">
-        <v>23</v>
       </c>
       <c r="D214" t="s">
         <v>47</v>
@@ -15629,11 +15629,11 @@
       <c r="A215" t="s">
         <v>276</v>
       </c>
-      <c r="B215">
+      <c r="B215" t="s">
+        <v>32</v>
+      </c>
+      <c r="C215">
         <v>7.7</v>
-      </c>
-      <c r="C215" t="s">
-        <v>32</v>
       </c>
       <c r="D215" t="s">
         <v>53</v>
@@ -15684,11 +15684,11 @@
       <c r="A216" t="s">
         <v>277</v>
       </c>
-      <c r="B216">
+      <c r="B216" t="s">
+        <v>27</v>
+      </c>
+      <c r="C216">
         <v>9.1999999999999993</v>
-      </c>
-      <c r="C216" t="s">
-        <v>27</v>
       </c>
       <c r="D216" t="s">
         <v>834</v>
@@ -15739,11 +15739,11 @@
       <c r="A217" t="s">
         <v>278</v>
       </c>
-      <c r="B217">
+      <c r="B217" t="s">
+        <v>27</v>
+      </c>
+      <c r="C217">
         <v>9</v>
-      </c>
-      <c r="C217" t="s">
-        <v>27</v>
       </c>
       <c r="D217" t="s">
         <v>837</v>
@@ -15797,11 +15797,11 @@
       <c r="A218" t="s">
         <v>279</v>
       </c>
-      <c r="B218">
+      <c r="B218" t="s">
+        <v>27</v>
+      </c>
+      <c r="C218">
         <v>9.5</v>
-      </c>
-      <c r="C218" t="s">
-        <v>27</v>
       </c>
       <c r="D218" t="s">
         <v>840</v>
@@ -15852,11 +15852,11 @@
       <c r="A219" t="s">
         <v>280</v>
       </c>
-      <c r="B219">
+      <c r="B219" t="s">
+        <v>27</v>
+      </c>
+      <c r="C219">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C219" t="s">
-        <v>27</v>
       </c>
       <c r="D219" t="s">
         <v>843</v>
@@ -15910,7 +15910,7 @@
       <c r="A220" t="s">
         <v>281</v>
       </c>
-      <c r="B220">
+      <c r="C220">
         <v>7.4</v>
       </c>
       <c r="D220" t="s">
@@ -15962,11 +15962,11 @@
       <c r="A221" t="s">
         <v>282</v>
       </c>
-      <c r="B221">
+      <c r="B221" t="s">
+        <v>27</v>
+      </c>
+      <c r="C221">
         <v>8.6</v>
-      </c>
-      <c r="C221" t="s">
-        <v>27</v>
       </c>
       <c r="D221" t="s">
         <v>849</v>
@@ -16017,11 +16017,11 @@
       <c r="A222" t="s">
         <v>283</v>
       </c>
-      <c r="B222">
+      <c r="B222" t="s">
+        <v>27</v>
+      </c>
+      <c r="C222">
         <v>8.6</v>
-      </c>
-      <c r="C222" t="s">
-        <v>27</v>
       </c>
       <c r="D222" t="s">
         <v>852</v>
@@ -16060,11 +16060,11 @@
       <c r="A223" t="s">
         <v>284</v>
       </c>
-      <c r="B223">
+      <c r="B223" t="s">
+        <v>27</v>
+      </c>
+      <c r="C223">
         <v>9.1</v>
-      </c>
-      <c r="C223" t="s">
-        <v>27</v>
       </c>
       <c r="D223" t="s">
         <v>855</v>
@@ -16118,11 +16118,11 @@
       <c r="A224" t="s">
         <v>285</v>
       </c>
-      <c r="B224">
+      <c r="B224" t="s">
+        <v>27</v>
+      </c>
+      <c r="C224">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C224" t="s">
-        <v>27</v>
       </c>
       <c r="D224" t="s">
         <v>857</v>
@@ -16176,11 +16176,11 @@
       <c r="A225" t="s">
         <v>286</v>
       </c>
-      <c r="B225">
+      <c r="B225" t="s">
+        <v>32</v>
+      </c>
+      <c r="C225">
         <v>7.8</v>
-      </c>
-      <c r="C225" t="s">
-        <v>32</v>
       </c>
       <c r="D225" t="s">
         <v>859</v>
@@ -16231,11 +16231,11 @@
       <c r="A226" t="s">
         <v>287</v>
       </c>
-      <c r="B226">
+      <c r="B226" t="s">
+        <v>27</v>
+      </c>
+      <c r="C226">
         <v>9.1999999999999993</v>
-      </c>
-      <c r="C226" t="s">
-        <v>27</v>
       </c>
       <c r="D226" t="s">
         <v>862</v>
@@ -16289,7 +16289,7 @@
       <c r="A227" t="s">
         <v>288</v>
       </c>
-      <c r="B227">
+      <c r="C227">
         <v>7.1</v>
       </c>
       <c r="D227" t="s">
@@ -16341,7 +16341,7 @@
       <c r="A228" t="s">
         <v>289</v>
       </c>
-      <c r="B228">
+      <c r="C228">
         <v>7.1</v>
       </c>
       <c r="D228" t="s">
@@ -16396,11 +16396,11 @@
       <c r="A229" t="s">
         <v>290</v>
       </c>
-      <c r="B229">
+      <c r="B229" t="s">
+        <v>27</v>
+      </c>
+      <c r="C229">
         <v>9.1</v>
-      </c>
-      <c r="C229" t="s">
-        <v>27</v>
       </c>
       <c r="D229" t="s">
         <v>868</v>
@@ -16454,11 +16454,11 @@
       <c r="A230" t="s">
         <v>291</v>
       </c>
-      <c r="B230">
+      <c r="B230" t="s">
+        <v>32</v>
+      </c>
+      <c r="C230">
         <v>7.8</v>
-      </c>
-      <c r="C230" t="s">
-        <v>32</v>
       </c>
       <c r="D230" t="s">
         <v>871</v>
@@ -16509,11 +16509,11 @@
       <c r="A231" t="s">
         <v>292</v>
       </c>
-      <c r="B231">
+      <c r="B231" t="s">
+        <v>27</v>
+      </c>
+      <c r="C231">
         <v>9</v>
-      </c>
-      <c r="C231" t="s">
-        <v>27</v>
       </c>
       <c r="D231" t="s">
         <v>873</v>
@@ -16564,11 +16564,11 @@
       <c r="A232" t="s">
         <v>293</v>
       </c>
-      <c r="B232">
+      <c r="B232" t="s">
+        <v>27</v>
+      </c>
+      <c r="C232">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C232" t="s">
-        <v>27</v>
       </c>
       <c r="D232" t="s">
         <v>876</v>
@@ -16619,11 +16619,11 @@
       <c r="A233" t="s">
         <v>294</v>
       </c>
-      <c r="B233">
+      <c r="B233" t="s">
+        <v>27</v>
+      </c>
+      <c r="C233">
         <v>8.9</v>
-      </c>
-      <c r="C233" t="s">
-        <v>27</v>
       </c>
       <c r="D233" t="s">
         <v>878</v>
@@ -16677,7 +16677,7 @@
       <c r="A234" t="s">
         <v>295</v>
       </c>
-      <c r="B234">
+      <c r="C234">
         <v>6.4</v>
       </c>
       <c r="D234" t="s">
@@ -16732,7 +16732,7 @@
       <c r="A235" t="s">
         <v>296</v>
       </c>
-      <c r="B235">
+      <c r="C235">
         <v>6.9</v>
       </c>
       <c r="D235" t="s">
@@ -16784,11 +16784,11 @@
       <c r="A236" t="s">
         <v>297</v>
       </c>
-      <c r="B236">
+      <c r="B236" t="s">
+        <v>27</v>
+      </c>
+      <c r="C236">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="C236" t="s">
-        <v>27</v>
       </c>
       <c r="D236" t="s">
         <v>883</v>
@@ -16842,11 +16842,11 @@
       <c r="A237" t="s">
         <v>298</v>
       </c>
-      <c r="B237">
+      <c r="B237" t="s">
+        <v>27</v>
+      </c>
+      <c r="C237">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C237" t="s">
-        <v>27</v>
       </c>
       <c r="D237" t="s">
         <v>886</v>
@@ -16897,11 +16897,11 @@
       <c r="A238" t="s">
         <v>299</v>
       </c>
-      <c r="B238">
+      <c r="B238" t="s">
+        <v>27</v>
+      </c>
+      <c r="C238">
         <v>8.9</v>
-      </c>
-      <c r="C238" t="s">
-        <v>27</v>
       </c>
       <c r="D238" t="s">
         <v>889</v>
@@ -16955,11 +16955,11 @@
       <c r="A239" t="s">
         <v>300</v>
       </c>
-      <c r="B239">
+      <c r="B239" t="s">
+        <v>27</v>
+      </c>
+      <c r="C239">
         <v>9.4</v>
-      </c>
-      <c r="C239" t="s">
-        <v>27</v>
       </c>
       <c r="D239" t="s">
         <v>891</v>
@@ -17013,11 +17013,11 @@
       <c r="A240" t="s">
         <v>301</v>
       </c>
-      <c r="B240">
+      <c r="B240" t="s">
+        <v>32</v>
+      </c>
+      <c r="C240">
         <v>7.6</v>
-      </c>
-      <c r="C240" t="s">
-        <v>32</v>
       </c>
       <c r="D240" t="s">
         <v>894</v>
@@ -17071,11 +17071,11 @@
       <c r="A241" t="s">
         <v>302</v>
       </c>
-      <c r="B241">
+      <c r="B241" t="s">
+        <v>27</v>
+      </c>
+      <c r="C241">
         <v>9.1</v>
-      </c>
-      <c r="C241" t="s">
-        <v>27</v>
       </c>
       <c r="D241" t="s">
         <v>896</v>
@@ -17129,11 +17129,11 @@
       <c r="A242" t="s">
         <v>303</v>
       </c>
-      <c r="B242">
+      <c r="B242" t="s">
+        <v>27</v>
+      </c>
+      <c r="C242">
         <v>8.6999999999999993</v>
-      </c>
-      <c r="C242" t="s">
-        <v>27</v>
       </c>
       <c r="D242" t="s">
         <v>898</v>
@@ -17187,11 +17187,11 @@
       <c r="A243" t="s">
         <v>304</v>
       </c>
-      <c r="B243">
+      <c r="B243" t="s">
+        <v>27</v>
+      </c>
+      <c r="C243">
         <v>9.5</v>
-      </c>
-      <c r="C243" t="s">
-        <v>27</v>
       </c>
       <c r="D243" t="s">
         <v>901</v>
@@ -17245,11 +17245,11 @@
       <c r="A244" t="s">
         <v>305</v>
       </c>
-      <c r="B244">
+      <c r="B244" t="s">
+        <v>32</v>
+      </c>
+      <c r="C244">
         <v>7.7</v>
-      </c>
-      <c r="C244" t="s">
-        <v>32</v>
       </c>
       <c r="D244" t="s">
         <v>904</v>
@@ -17303,7 +17303,7 @@
       <c r="A245" t="s">
         <v>306</v>
       </c>
-      <c r="B245">
+      <c r="C245">
         <v>5.7</v>
       </c>
       <c r="D245" t="s">
@@ -17355,11 +17355,11 @@
       <c r="A246" t="s">
         <v>307</v>
       </c>
-      <c r="B246">
+      <c r="B246" t="s">
+        <v>27</v>
+      </c>
+      <c r="C246">
         <v>9.1</v>
-      </c>
-      <c r="C246" t="s">
-        <v>27</v>
       </c>
       <c r="D246" t="s">
         <v>908</v>
@@ -17408,7 +17408,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <sortState ref="A2:T789">
+  <sortState ref="A2:U789">
     <sortCondition ref="S2:S789"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
